--- a/artfynd/A 29717-2024 artfynd.xlsx
+++ b/artfynd/A 29717-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129874925</v>
       </c>
       <c r="B2" t="n">
-        <v>78838</v>
+        <v>78841</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129874927</v>
+        <v>129874924</v>
       </c>
       <c r="B3" t="n">
-        <v>78839</v>
+        <v>78841</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454620</v>
+        <v>454584</v>
       </c>
       <c r="R3" t="n">
-        <v>6893593</v>
+        <v>6893588</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129874924</v>
+        <v>129874927</v>
       </c>
       <c r="B4" t="n">
-        <v>78838</v>
+        <v>78842</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454584</v>
+        <v>454620</v>
       </c>
       <c r="R4" t="n">
-        <v>6893588</v>
+        <v>6893593</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 29717-2024 artfynd.xlsx
+++ b/artfynd/A 29717-2024 artfynd.xlsx
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129874924</v>
+        <v>129874927</v>
       </c>
       <c r="B3" t="n">
-        <v>78841</v>
+        <v>78842</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454584</v>
+        <v>454620</v>
       </c>
       <c r="R3" t="n">
-        <v>6893588</v>
+        <v>6893593</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129874927</v>
+        <v>129874924</v>
       </c>
       <c r="B4" t="n">
-        <v>78842</v>
+        <v>78841</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454620</v>
+        <v>454584</v>
       </c>
       <c r="R4" t="n">
-        <v>6893593</v>
+        <v>6893588</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 29717-2024 artfynd.xlsx
+++ b/artfynd/A 29717-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129874925</v>
       </c>
       <c r="B2" t="n">
-        <v>78841</v>
+        <v>78844</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129874927</v>
+        <v>129874924</v>
       </c>
       <c r="B3" t="n">
-        <v>78842</v>
+        <v>78844</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454620</v>
+        <v>454584</v>
       </c>
       <c r="R3" t="n">
-        <v>6893593</v>
+        <v>6893588</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129874924</v>
+        <v>129874927</v>
       </c>
       <c r="B4" t="n">
-        <v>78841</v>
+        <v>78845</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454584</v>
+        <v>454620</v>
       </c>
       <c r="R4" t="n">
-        <v>6893588</v>
+        <v>6893593</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 29717-2024 artfynd.xlsx
+++ b/artfynd/A 29717-2024 artfynd.xlsx
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129874924</v>
+        <v>129874927</v>
       </c>
       <c r="B3" t="n">
-        <v>78844</v>
+        <v>78845</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454584</v>
+        <v>454620</v>
       </c>
       <c r="R3" t="n">
-        <v>6893588</v>
+        <v>6893593</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129874927</v>
+        <v>129874924</v>
       </c>
       <c r="B4" t="n">
-        <v>78845</v>
+        <v>78844</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454620</v>
+        <v>454584</v>
       </c>
       <c r="R4" t="n">
-        <v>6893593</v>
+        <v>6893588</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 29717-2024 artfynd.xlsx
+++ b/artfynd/A 29717-2024 artfynd.xlsx
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129874927</v>
+        <v>129874924</v>
       </c>
       <c r="B3" t="n">
-        <v>78845</v>
+        <v>78844</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454620</v>
+        <v>454584</v>
       </c>
       <c r="R3" t="n">
-        <v>6893593</v>
+        <v>6893588</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129874924</v>
+        <v>129874927</v>
       </c>
       <c r="B4" t="n">
-        <v>78844</v>
+        <v>78845</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454584</v>
+        <v>454620</v>
       </c>
       <c r="R4" t="n">
-        <v>6893588</v>
+        <v>6893593</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 29717-2024 artfynd.xlsx
+++ b/artfynd/A 29717-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129874925</v>
       </c>
       <c r="B2" t="n">
-        <v>78844</v>
+        <v>78845</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129874924</v>
+        <v>129874927</v>
       </c>
       <c r="B3" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454584</v>
+        <v>454620</v>
       </c>
       <c r="R3" t="n">
-        <v>6893588</v>
+        <v>6893593</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,7 +877,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129874927</v>
+        <v>129874924</v>
       </c>
       <c r="B4" t="n">
         <v>78845</v>
@@ -888,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454620</v>
+        <v>454584</v>
       </c>
       <c r="R4" t="n">
-        <v>6893593</v>
+        <v>6893588</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 29717-2024 artfynd.xlsx
+++ b/artfynd/A 29717-2024 artfynd.xlsx
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129874927</v>
+        <v>129874924</v>
       </c>
       <c r="B3" t="n">
-        <v>78846</v>
+        <v>78845</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454620</v>
+        <v>454584</v>
       </c>
       <c r="R3" t="n">
-        <v>6893593</v>
+        <v>6893588</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129874924</v>
+        <v>129874927</v>
       </c>
       <c r="B4" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454584</v>
+        <v>454620</v>
       </c>
       <c r="R4" t="n">
-        <v>6893588</v>
+        <v>6893593</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 29717-2024 artfynd.xlsx
+++ b/artfynd/A 29717-2024 artfynd.xlsx
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129874924</v>
+        <v>129874927</v>
       </c>
       <c r="B3" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454584</v>
+        <v>454620</v>
       </c>
       <c r="R3" t="n">
-        <v>6893588</v>
+        <v>6893593</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129874927</v>
+        <v>129874924</v>
       </c>
       <c r="B4" t="n">
-        <v>78846</v>
+        <v>78845</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454620</v>
+        <v>454584</v>
       </c>
       <c r="R4" t="n">
-        <v>6893593</v>
+        <v>6893588</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 29717-2024 artfynd.xlsx
+++ b/artfynd/A 29717-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129874925</v>
       </c>
       <c r="B2" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129874927</v>
+        <v>129874924</v>
       </c>
       <c r="B3" t="n">
         <v>78846</v>
@@ -787,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454620</v>
+        <v>454584</v>
       </c>
       <c r="R3" t="n">
-        <v>6893593</v>
+        <v>6893588</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129874924</v>
+        <v>129874927</v>
       </c>
       <c r="B4" t="n">
-        <v>78845</v>
+        <v>78847</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454584</v>
+        <v>454620</v>
       </c>
       <c r="R4" t="n">
-        <v>6893588</v>
+        <v>6893593</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 29717-2024 artfynd.xlsx
+++ b/artfynd/A 29717-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129874925</v>
       </c>
       <c r="B2" t="n">
-        <v>78852</v>
+        <v>78937</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129874924</v>
+        <v>129874927</v>
       </c>
       <c r="B3" t="n">
-        <v>78852</v>
+        <v>78938</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454584</v>
+        <v>454620</v>
       </c>
       <c r="R3" t="n">
-        <v>6893588</v>
+        <v>6893593</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129874927</v>
+        <v>129874924</v>
       </c>
       <c r="B4" t="n">
-        <v>78853</v>
+        <v>78937</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454620</v>
+        <v>454584</v>
       </c>
       <c r="R4" t="n">
-        <v>6893593</v>
+        <v>6893588</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 29717-2024 artfynd.xlsx
+++ b/artfynd/A 29717-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129874925</v>
       </c>
       <c r="B2" t="n">
-        <v>78937</v>
+        <v>78852</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129874927</v>
+        <v>129874924</v>
       </c>
       <c r="B3" t="n">
-        <v>78938</v>
+        <v>78852</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454620</v>
+        <v>454584</v>
       </c>
       <c r="R3" t="n">
-        <v>6893593</v>
+        <v>6893588</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129874924</v>
+        <v>129874927</v>
       </c>
       <c r="B4" t="n">
-        <v>78937</v>
+        <v>78853</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454584</v>
+        <v>454620</v>
       </c>
       <c r="R4" t="n">
-        <v>6893588</v>
+        <v>6893593</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 29717-2024 artfynd.xlsx
+++ b/artfynd/A 29717-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129874925</v>
+        <v>129874923</v>
       </c>
       <c r="B2" t="n">
-        <v>78852</v>
+        <v>79084</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>454620</v>
+        <v>454745</v>
       </c>
       <c r="R2" t="n">
-        <v>6893593</v>
+        <v>6893737</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -779,7 +779,7 @@
         <v>129874924</v>
       </c>
       <c r="B3" t="n">
-        <v>78852</v>
+        <v>79084</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129874927</v>
+        <v>129874925</v>
       </c>
       <c r="B4" t="n">
-        <v>78853</v>
+        <v>79084</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -971,6 +971,428 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr">
+        <is>
+          <t>NNK kartering 2025, Länsstyrelsen Jämtlands län.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129874929</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Gullhög-Tönningfloarna, Hjd</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>454326</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6893239</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>16:23</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>16:23</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Anton Gårdman</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Anton Gårdman</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>NNK kartering 2025, Länsstyrelsen Jämtlands län.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129874922</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Gullhög-Tönningfloarna, Hjd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>454745</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6893737</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Anton Gårdman</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anton Gårdman</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>NNK kartering 2025, Länsstyrelsen Jämtlands län.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129874927</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Gullhög-Tönningfloarna, Hjd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>454620</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6893593</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Anton Gårdman</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anton Gårdman</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>NNK kartering 2025, Länsstyrelsen Jämtlands län.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129874928</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Gullhög-Tönningfloarna, Hjd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>454648</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6893577</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Anton Gårdman</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Anton Gårdman</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
         <is>
           <t>NNK kartering 2025, Länsstyrelsen Jämtlands län.</t>
         </is>

--- a/artfynd/A 29717-2024 artfynd.xlsx
+++ b/artfynd/A 29717-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>NNK kartering 2025, Länsstyrelsen Jämtlands län.</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129874923</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>NNK kartering 2025, Länsstyrelsen Jämtlands län.</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129874924</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>NNK kartering 2025, Länsstyrelsen Jämtlands län.</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129874925</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1094,6 +1114,11 @@
           <t>NNK kartering 2025, Länsstyrelsen Jämtlands län.</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129874929</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1195,6 +1220,11 @@
           <t>NNK kartering 2025, Länsstyrelsen Jämtlands län.</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129874922</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1296,6 +1326,11 @@
           <t>NNK kartering 2025, Länsstyrelsen Jämtlands län.</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129874927</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1397,8 +1432,22 @@
           <t>NNK kartering 2025, Länsstyrelsen Jämtlands län.</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129874928</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>